--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.160" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.160" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.160.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.160.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0160.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0160.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.160.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.160" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.160" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,23 +416,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y120"/>
+  <dimension ref="A1:Y122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="49" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -595,14 +595,22 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]153</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]153</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 153</t>
@@ -610,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L7: isolated marker/symbol line :: t</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]153</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -641,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -650,10 +658,14 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L136: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L135: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L135: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -665,7 +677,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L17: symbol-only separator/garbage line :: .50</t>
+          <t>L7: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -716,7 +728,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: 10</t>
+          <t>L17: symbol-only separator/garbage line :: .50</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -742,12 +754,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -767,7 +779,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L21: symbol-only separator/garbage line :: .5 0</t>
+          <t>L19: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -818,7 +830,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L22: isolated marker/symbol line :: 50</t>
+          <t>L21: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -869,7 +881,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L24: symbol-only separator/garbage line :: - 0 0</t>
+          <t>L22: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -920,7 +932,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L24: symbol-only separator/garbage line :: - 0 0</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -967,7 +979,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: 10</t>
+          <t>L26: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -989,7 +1001,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1014,7 +1026,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: F,</t>
+          <t>L83: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1041,7 +1053,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1061,7 +1073,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L87: symbol-only separator/garbage line :: 10 0</t>
+          <t>L85: isolated marker/symbol line :: F,</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1083,12 +1095,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1108,7 +1120,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L91: symbol-only separator/garbage line :: &gt; 10 0</t>
+          <t>L87: symbol-only separator/garbage line :: 10 0</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1155,7 +1167,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L93: symbol-only separator/garbage line :: 25 0</t>
+          <t>L91: symbol-only separator/garbage line :: &gt; 10 0</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1202,7 +1214,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: r</t>
+          <t>L93: symbol-only separator/garbage line :: 25 0</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1249,7 +1261,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L96: symbol-only separator/garbage line :: )42 0</t>
+          <t>L95: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1296,7 +1308,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 10</t>
+          <t>L96: symbol-only separator/garbage line :: )42 0</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1343,7 +1355,7 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: e</t>
+          <t>L98: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1378,7 +1390,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 13</t>
+          <t>L100: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1413,7 +1425,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L106: symbol-only separator/garbage line :: ,10</t>
+          <t>L105: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1448,7 +1460,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L107: symbol-only separator/garbage line :: .10</t>
+          <t>L106: symbol-only separator/garbage line :: ,10</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1483,7 +1495,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: r</t>
+          <t>L107: symbol-only separator/garbage line :: .10</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1518,7 +1530,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L111: symbol-only separator/garbage line :: .5 0</t>
+          <t>L108: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1553,7 +1565,7 @@
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L113: symbol-only separator/garbage line :: 5 0</t>
+          <t>L111: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: A</t>
+          <t>L113: symbol-only separator/garbage line :: 5 0</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1623,7 +1635,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: 10</t>
+          <t>L115: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1658,7 +1670,7 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L118: symbol-only separator/garbage line :: .10</t>
+          <t>L117: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1693,7 +1705,7 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L120: symbol-only separator/garbage line :: 0 6</t>
+          <t>L118: symbol-only separator/garbage line :: .10</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1728,7 +1740,7 @@
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L121: symbol-only separator/garbage line :: .5 0</t>
+          <t>L120: symbol-only separator/garbage line :: 0 6</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1763,7 +1775,7 @@
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L123: symbol-only separator/garbage line :: 5 0</t>
+          <t>L121: symbol-only separator/garbage line :: .5 0</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1798,7 +1810,7 @@
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L125: symbol-only separator/garbage line :: .2 6</t>
+          <t>L123: symbol-only separator/garbage line :: 5 0</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1833,7 +1845,7 @@
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: 04</t>
+          <t>L125: symbol-only separator/garbage line :: .2 6</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1868,7 +1880,7 @@
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L129: symbol-only separator/garbage line :: .50</t>
+          <t>L127: isolated marker/symbol line :: 04</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1903,7 +1915,7 @@
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L131: symbol-only separator/garbage line :: 1 3</t>
+          <t>L129: symbol-only separator/garbage line :: .50</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -1938,7 +1950,7 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: L</t>
+          <t>L131: symbol-only separator/garbage line :: 1 3</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -1968,12 +1980,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 2</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L135: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L133: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2003,10 +2015,14 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 6</t>
-        </is>
-      </c>
-      <c r="O36" s="1" t="inlineStr"/>
+          <t>L61: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L135: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
       <c r="R36" s="1" t="inlineStr"/>
@@ -2034,7 +2050,7 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: 1</t>
+          <t>L62: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -2065,7 +2081,7 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 0</t>
+          <t>L66: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2096,7 +2112,7 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 1</t>
+          <t>L67: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2127,7 +2143,7 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 0</t>
+          <t>L69: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2158,7 +2174,7 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: 1</t>
+          <t>L70: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2189,7 +2205,7 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 3</t>
+          <t>L72: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2220,7 +2236,7 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: 1</t>
+          <t>L73: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2251,7 +2267,7 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 0</t>
+          <t>L75: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2282,7 +2298,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 1</t>
+          <t>L76: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2313,7 +2329,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 3</t>
+          <t>L78: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2344,7 +2360,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 1</t>
+          <t>L79: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2375,7 +2391,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 0</t>
+          <t>L80: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2406,7 +2422,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: 1</t>
+          <t>L81: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2437,7 +2453,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 3</t>
+          <t>L83: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2468,7 +2484,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: r</t>
+          <t>L84: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2499,7 +2515,7 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: 2</t>
+          <t>L85: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -2530,7 +2546,7 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 6</t>
+          <t>L87: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -2561,7 +2577,7 @@
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 0</t>
+          <t>L88: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -2592,7 +2608,7 @@
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 6</t>
+          <t>L89: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -2623,7 +2639,7 @@
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: 1</t>
+          <t>L90: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -2654,7 +2670,7 @@
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 2</t>
+          <t>L91: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -2685,7 +2701,7 @@
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 0</t>
+          <t>L93: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -2716,7 +2732,7 @@
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 5</t>
+          <t>L94: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -2747,7 +2763,7 @@
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 0</t>
+          <t>L95: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -2778,7 +2794,7 @@
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 2</t>
+          <t>L96: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -2809,7 +2825,7 @@
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 6</t>
+          <t>L98: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -2840,7 +2856,7 @@
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: 5</t>
+          <t>L99: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -2871,7 +2887,7 @@
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 0</t>
+          <t>L100: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -2902,7 +2918,7 @@
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: 1</t>
+          <t>L101: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -2933,7 +2949,7 @@
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 0</t>
+          <t>L104: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -2964,7 +2980,7 @@
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: 5</t>
+          <t>L105: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -2995,7 +3011,7 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: 0</t>
+          <t>L106: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3026,7 +3042,7 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L109: isolated marker/symbol line :: 1</t>
+          <t>L107: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3057,7 +3073,7 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: 0</t>
+          <t>L109: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3088,7 +3104,7 @@
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: 2</t>
+          <t>L110: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -3119,7 +3135,7 @@
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: 6</t>
+          <t>L111: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -3150,7 +3166,7 @@
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L114: isolated marker/symbol line :: 0</t>
+          <t>L112: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -3181,7 +3197,7 @@
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: 6</t>
+          <t>L114: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -3212,7 +3228,7 @@
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 0</t>
+          <t>L115: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -3243,7 +3259,7 @@
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: 4</t>
+          <t>L116: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
@@ -3274,7 +3290,7 @@
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L119: isolated marker/symbol line :: 5</t>
+          <t>L117: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr"/>
@@ -3305,7 +3321,7 @@
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L120: isolated marker/symbol line :: 0</t>
+          <t>L119: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr"/>
@@ -3336,7 +3352,7 @@
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: 5</t>
+          <t>L120: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr"/>
@@ -3367,7 +3383,7 @@
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: 0</t>
+          <t>L121: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr"/>
@@ -3398,7 +3414,7 @@
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L123: isolated marker/symbol line :: 10</t>
+          <t>L122: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr"/>
@@ -3429,7 +3445,7 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 0</t>
+          <t>L123: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr"/>
@@ -3460,7 +3476,7 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: ,</t>
+          <t>L124: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr"/>
@@ -3491,7 +3507,7 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: 10</t>
+          <t>L126: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -3522,7 +3538,7 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L128: isolated marker/symbol line :: 0</t>
+          <t>L127: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -3553,7 +3569,7 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L129: isolated marker/symbol line :: 25</t>
+          <t>L128: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -3584,7 +3600,7 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: 0</t>
+          <t>L129: isolated marker/symbol line :: 25</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -3615,7 +3631,7 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: r</t>
+          <t>L130: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -3646,7 +3662,7 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L132: isolated marker/symbol line :: 42</t>
+          <t>L131: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -3677,7 +3693,7 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: 0</t>
+          <t>L132: isolated marker/symbol line :: 42</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -3708,7 +3724,7 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L138: isolated marker/symbol line :: 1</t>
+          <t>L133: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -3739,7 +3755,7 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: 3</t>
+          <t>L136: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -3770,7 +3786,7 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 1</t>
+          <t>L138: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -3801,7 +3817,7 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L141: isolated marker/symbol line :: 0</t>
+          <t>L139: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -3832,7 +3848,7 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L142: isolated marker/symbol line :: 1</t>
+          <t>L140: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -3863,7 +3879,7 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L143: isolated marker/symbol line :: 0</t>
+          <t>L141: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -3894,7 +3910,7 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L144: isolated marker/symbol line :: r</t>
+          <t>L142: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -3925,7 +3941,7 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L145: isolated marker/symbol line :: 0</t>
+          <t>L143: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -3956,7 +3972,7 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: 6</t>
+          <t>L144: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -3987,7 +4003,7 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L147: isolated marker/symbol line :: 5</t>
+          <t>L145: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -4018,7 +4034,7 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L148: isolated marker/symbol line :: 0</t>
+          <t>L146: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -4049,7 +4065,7 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L149: isolated marker/symbol line :: 5</t>
+          <t>L147: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -4080,7 +4096,7 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: 0</t>
+          <t>L148: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -4111,7 +4127,7 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L152: isolated marker/symbol line :: 5</t>
+          <t>L149: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -4142,7 +4158,7 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L153: isolated marker/symbol line :: 0</t>
+          <t>L150: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -4173,7 +4189,7 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L154: isolated marker/symbol line :: 5</t>
+          <t>L152: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -4204,7 +4220,7 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L155: isolated marker/symbol line :: 0</t>
+          <t>L153: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -4235,7 +4251,7 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L156: isolated marker/symbol line :: 0</t>
+          <t>L154: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -4266,7 +4282,7 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L157: isolated marker/symbol line :: 0</t>
+          <t>L155: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -4297,7 +4313,7 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L158: symbol-only separator/garbage line :: 1 3</t>
+          <t>L156: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -4328,7 +4344,7 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L159: symbol-only separator/garbage line :: 1 3</t>
+          <t>L157: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -4359,7 +4375,7 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L160: isolated marker/symbol line :: L</t>
+          <t>L158: symbol-only separator/garbage line :: 1 3</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -4390,7 +4406,7 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L161: isolated marker/symbol line :: 5</t>
+          <t>L159: symbol-only separator/garbage line :: 1 3</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -4421,7 +4437,7 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L162: isolated marker/symbol line :: 0</t>
+          <t>L160: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -4452,7 +4468,7 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L163: isolated marker/symbol line :: 2</t>
+          <t>L161: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -4483,7 +4499,7 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L164: isolated marker/symbol line :: 6</t>
+          <t>L162: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -4514,7 +4530,7 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L165: isolated marker/symbol line :: 0</t>
+          <t>L163: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -4545,7 +4561,7 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L166: isolated marker/symbol line :: 4</t>
+          <t>L164: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -4576,7 +4592,7 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L167: isolated marker/symbol line :: 5</t>
+          <t>L165: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -4607,7 +4623,7 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L168: isolated marker/symbol line :: 0</t>
+          <t>L166: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -4622,6 +4638,68 @@
       <c r="X120" s="1" t="inlineStr"/>
       <c r="Y120" s="1" t="inlineStr"/>
     </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr"/>
+      <c r="B121" s="1" t="inlineStr"/>
+      <c r="C121" s="1" t="inlineStr"/>
+      <c r="D121" s="1" t="inlineStr"/>
+      <c r="E121" s="1" t="inlineStr"/>
+      <c r="F121" s="1" t="inlineStr"/>
+      <c r="G121" s="1" t="inlineStr"/>
+      <c r="H121" s="1" t="inlineStr"/>
+      <c r="I121" s="1" t="inlineStr"/>
+      <c r="J121" s="1" t="inlineStr"/>
+      <c r="K121" s="1" t="inlineStr"/>
+      <c r="L121" s="1" t="inlineStr"/>
+      <c r="M121" s="1" t="inlineStr"/>
+      <c r="N121" s="1" t="inlineStr">
+        <is>
+          <t>L167: isolated marker/symbol line :: 5</t>
+        </is>
+      </c>
+      <c r="O121" s="1" t="inlineStr"/>
+      <c r="P121" s="1" t="inlineStr"/>
+      <c r="Q121" s="1" t="inlineStr"/>
+      <c r="R121" s="1" t="inlineStr"/>
+      <c r="S121" s="1" t="inlineStr"/>
+      <c r="T121" s="1" t="inlineStr"/>
+      <c r="U121" s="1" t="inlineStr"/>
+      <c r="V121" s="1" t="inlineStr"/>
+      <c r="W121" s="1" t="inlineStr"/>
+      <c r="X121" s="1" t="inlineStr"/>
+      <c r="Y121" s="1" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr"/>
+      <c r="B122" s="1" t="inlineStr"/>
+      <c r="C122" s="1" t="inlineStr"/>
+      <c r="D122" s="1" t="inlineStr"/>
+      <c r="E122" s="1" t="inlineStr"/>
+      <c r="F122" s="1" t="inlineStr"/>
+      <c r="G122" s="1" t="inlineStr"/>
+      <c r="H122" s="1" t="inlineStr"/>
+      <c r="I122" s="1" t="inlineStr"/>
+      <c r="J122" s="1" t="inlineStr"/>
+      <c r="K122" s="1" t="inlineStr"/>
+      <c r="L122" s="1" t="inlineStr"/>
+      <c r="M122" s="1" t="inlineStr"/>
+      <c r="N122" s="1" t="inlineStr">
+        <is>
+          <t>L168: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O122" s="1" t="inlineStr"/>
+      <c r="P122" s="1" t="inlineStr"/>
+      <c r="Q122" s="1" t="inlineStr"/>
+      <c r="R122" s="1" t="inlineStr"/>
+      <c r="S122" s="1" t="inlineStr"/>
+      <c r="T122" s="1" t="inlineStr"/>
+      <c r="U122" s="1" t="inlineStr"/>
+      <c r="V122" s="1" t="inlineStr"/>
+      <c r="W122" s="1" t="inlineStr"/>
+      <c r="X122" s="1" t="inlineStr"/>
+      <c r="Y122" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
